--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3134-170-CM26</t>
+          <t>4280-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15079.44</v>
+        <v>31930.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>568658-134-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>46156.53</v>
+        <v>31420.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>2696-9-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,6 +691,1966 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
+        <v>6157.54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4301-172-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>30183.16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1035206-28-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65.165.411-4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>7694.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3134-35-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>15091.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4290-35-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>8508.02</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4766-110-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.060.200-8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>13316.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2427-269-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>55977.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3776-186-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>10652.88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1048-146-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>35421.54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3073-229-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.102.015-5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>8809.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3621-135-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.050.200-3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>16512.92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2424-942-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>980179.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3882-175-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.060.400-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>13316.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3157-36-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.102.016-3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>798.97</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-1019-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>6424.57</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3232-391-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>47158.09</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-1439-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>242260.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4555-190-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>10652.88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4044-655-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.061.800-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>53116.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2598-180-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>73.568.600-3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCON</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>4711.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4290-116-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>7735</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>859378-575-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>59500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1725-5533-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>346215.74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2594-926-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>73.568.600-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCON</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>5286.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3275-277-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>7401.62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>836-190-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>72.235.100-2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL V REGION</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>41563.37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3275-278-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>4440.97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3275-281-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>4229.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3275-282-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>37219.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2428-1603-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>62141.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3134-170-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>15079.44</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>836-127-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>72.235.100-2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL V REGION</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>46156.53</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1202333-127-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.060.700-K</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>27892.7</v>
       </c>
     </row>
